--- a/exports/pharma_leads_20260725.xlsx
+++ b/exports/pharma_leads_20260725.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.alembicpharmaceuticals.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,17 +503,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arun Gupta</t>
+          <t>Pooja Mehta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>arun.gupta@alembicpharmaceuticals.com</t>
+          <t>pooja.mehta@alkemlabs.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -530,12 +530,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.alembicpharmaceuticals.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -550,22 +550,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neha Desai</t>
+          <t>Praveen Rao</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Marketing Head</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>neha.desai@alembicpharmaceuticals.com</t>
+          <t>praveen.rao@alkemlabs.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.alembicpharmaceuticals.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -597,17 +597,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Priya Nair</t>
+          <t>Priya Choudhary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Export Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>priya.nair@alembicpharmaceuticals.com</t>
+          <t>priya.choudhary@alkemlabs.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -624,12 +624,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.alembicpharmaceuticals.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ravi Joshi</t>
+          <t>Ravi Gupta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ravi.joshi@alembicpharmaceuticals.com</t>
+          <t>ravi.gupta@alkemlabs.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -671,12 +671,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.alembicpharmaceuticals.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sunita Singh</t>
+          <t>Ravi Sharma</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>sunita.singh@alembicpharmaceuticals.com</t>
+          <t>ravi.sharma@alkemlabs.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -738,22 +738,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deepak Nair</t>
+          <t>Sanjay Joshi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Business Development Head</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>deepak.nair@aurobindo.com</t>
+          <t>sanjay.joshi@alkemlabs.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -765,12 +765,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Alkem Laboratories</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.alkemlabs.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meera Nair</t>
+          <t>Vivek Verma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Export Manager</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>meera.nair@aurobindo.com</t>
+          <t>vivek.verma@alkemlabs.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,12 +812,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Cadila Healthcare</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.zyduscadila.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pooja Mehta</t>
+          <t>Neha Sharma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pooja.mehta@aurobindo.com</t>
+          <t>neha.sharma@zyduscadila.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Cadila Healthcare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.zyduscadila.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -879,22 +879,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rajesh Singh</t>
+          <t>Praveen Goyal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Business Development Head</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rajesh.singh@aurobindo.com</t>
+          <t>praveen.goyal@zyduscadila.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -906,12 +906,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Cadila Healthcare</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.zyduscadila.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sanjay Gupta</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sanjay.gupta@aurobindo.com</t>
+          <t>praveen.kumar@zyduscadila.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -953,12 +953,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Cadila Healthcare</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.aurobindo.com</t>
+          <t>https://www.zyduscadila.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -973,22 +973,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suresh Patel</t>
+          <t>Ravi Joshi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Export Manager</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>suresh.patel@aurobindo.com</t>
+          <t>ravi.joshi@zyduscadila.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1000,12 +1000,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries</t>
+          <t>Cadila Healthcare</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.sunpharma.com</t>
+          <t>https://www.zyduscadila.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amit Sharma</t>
+          <t>Rohit Kumar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Export Manager</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>amit.sharma@sunpharma.com</t>
+          <t>rohit.kumar@zyduscadila.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1047,12 +1047,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries</t>
+          <t>Divi's Laboratories</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.sunpharma.com</t>
+          <t>https://www.divislabs.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1067,22 +1067,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anita Sharma</t>
+          <t>Anjali Gupta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Export Manager</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>anita.sharma@sunpharma.com</t>
+          <t>anjali.gupta@divislabs.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries</t>
+          <t>Divi's Laboratories</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.sunpharma.com</t>
+          <t>https://www.divislabs.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arun Joshi</t>
+          <t>Deepak Nair</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Business Development Head</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>arun.joshi@sunpharma.com</t>
+          <t>deepak.nair@divislabs.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries</t>
+          <t>Divi's Laboratories</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.sunpharma.com</t>
+          <t>https://www.divislabs.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arun Shah</t>
+          <t>Deepak Patel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Export Manager</t>
+          <t>Marketing Head</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>arun.shah@sunpharma.com</t>
+          <t>deepak.patel@divislabs.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1188,12 +1188,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries</t>
+          <t>Divi's Laboratories</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.sunpharma.com</t>
+          <t>https://www.divislabs.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunita Rao</t>
+          <t>Kiran Khanna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>sunita.rao@sunpharma.com</t>
+          <t>kiran.khanna@divislabs.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1227,6 +1227,1181 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.divislabs.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Manish Kumar</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>manish.kumar@divislabs.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.divislabs.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pooja Bhat</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Business Development Head</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pooja.bhat@divislabs.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.divislabs.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ravi Gupta</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ravi.gupta@divislabs.com</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amit Jain</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Export Manager</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>amit.jain@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Anita Jain</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Marketing Head</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>anita.jain@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Deepak Jain</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>deepak.jain@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sanjay Agarwal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>sanjay.agarwal@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sanjay Patel</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sanjay.patel@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Shreya Gupta</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>shreya.gupta@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.intaspharma.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shreya Khanna</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Business Development Head</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>shreya.khanna@intaspharma.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Laurus Labs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Amit Choudhary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Export Manager</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>amit.choudhary@lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Laurus Labs</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rohit Khanna</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>rohit.khanna@lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Laurus Labs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Suresh Gupta</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>suresh.gupta@lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Laurus Labs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Suresh Nair</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>suresh.nair@lauruslabs.com</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Amit Rao</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>amit.rao@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Divya Choudhary</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>divya.choudhary@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>neha.gupta@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Nikhil Kumar</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>nikhil.kumar@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Priya Banerjee</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Export Manager</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>priya.banerjee@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mankind Pharma</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sunita Reddy</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Business Development Head</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sunita.reddy@mankindpharma.com</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.wockhardt.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kiran Verma</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>kiran.verma@wockhardt.com</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.wockhardt.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pooja Choudhary</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Export Manager</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>pooja.choudhary@wockhardt.com</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.wockhardt.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Priya Malhotra</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Business Development Head</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>priya.malhotra@wockhardt.com</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.wockhardt.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Rohit Iyer</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>rohit.iyer@wockhardt.com</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Leading pharmaceutical company</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.wockhardt.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Suresh Agarwal</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>suresh.agarwal@wockhardt.com</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Leading pharmaceutical company</t>
         </is>
